--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.05641</v>
+        <v>17.09496</v>
       </c>
       <c r="D2" t="n">
-        <v>16.28989</v>
+        <v>16.50665</v>
       </c>
       <c r="E2" t="n">
-        <v>16.98962</v>
+        <v>16.96092</v>
       </c>
       <c r="F2" t="n">
-        <v>42.57651</v>
+        <v>42.71082</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05025</v>
+        <v>0.05036</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81924</v>
+        <v>1.81036</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.88685</v>
+        <v>16.61749</v>
       </c>
       <c r="D3" t="n">
-        <v>16.47525</v>
+        <v>16.45983</v>
       </c>
       <c r="E3" t="n">
-        <v>16.55628</v>
+        <v>16.4996</v>
       </c>
       <c r="F3" t="n">
-        <v>43.05875</v>
+        <v>42.36031</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05041</v>
+        <v>0.05093</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82811</v>
+        <v>1.81891</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.84639</v>
+        <v>16.82505</v>
       </c>
       <c r="D4" t="n">
-        <v>16.66023</v>
+        <v>16.31317</v>
       </c>
       <c r="E4" t="n">
-        <v>16.58647</v>
+        <v>16.77992</v>
       </c>
       <c r="F4" t="n">
-        <v>42.8886</v>
+        <v>43.35075</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05177</v>
+        <v>0.05136</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81624</v>
+        <v>1.84155</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.79725</v>
+        <v>16.87447</v>
       </c>
       <c r="D6" t="n">
-        <v>16.35996</v>
+        <v>15.80328</v>
       </c>
       <c r="E6" t="n">
-        <v>16.23556</v>
+        <v>16.7415</v>
       </c>
       <c r="F6" t="n">
-        <v>21.89065</v>
+        <v>22.19115</v>
       </c>
       <c r="G6" t="n">
-        <v>34.26527</v>
+        <v>34.54388</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.8318</v>
+        <v>17.23524</v>
       </c>
       <c r="D7" t="n">
-        <v>15.91829</v>
+        <v>16.13364</v>
       </c>
       <c r="E7" t="n">
-        <v>16.56204</v>
+        <v>16.62439</v>
       </c>
       <c r="F7" t="n">
-        <v>21.43397</v>
+        <v>21.75271</v>
       </c>
       <c r="G7" t="n">
-        <v>34.3203</v>
+        <v>34.44139</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.04953</v>
+        <v>16.82026</v>
       </c>
       <c r="D8" t="n">
-        <v>15.8916</v>
+        <v>16.51349</v>
       </c>
       <c r="E8" t="n">
-        <v>16.57369</v>
+        <v>16.58227</v>
       </c>
       <c r="F8" t="n">
-        <v>21.99568</v>
+        <v>21.70957</v>
       </c>
       <c r="G8" t="n">
-        <v>35.30503</v>
+        <v>34.0902</v>
       </c>
     </row>
   </sheetData>
